--- a/training_forms/016_hospital_ai_training_initiative_evaluation_form--training_forms.xlsx
+++ b/training_forms/016_hospital_ai_training_initiative_evaluation_form--training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Form Information</t>
+          <t>Overall Impressions</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Quality of Training Sessions</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Topics for Future Training Sessions</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Usefulness of Materials and Resources</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Positive Impact on Patient Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form Information</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Form Information</t>
+          <t>Suggestions for Improving the Program</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Frequency of Training and Updates</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Issues Encountered while Using AI System</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Features and Functionalities</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,126 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Form Information</t>
+          <t>Satisfaction with the Program</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Information</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Notes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Form Information</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -914,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -942,493 +827,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'Option 1'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'Option 2'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option_3'}</t>
+          <t>bi-monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'Option 3'}</t>
+          <t>Bi-Monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_4',_'value':_'option_4'}</t>
+          <t>feature_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 4', 'value': 'Option 4'}</t>
+          <t>Feature A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_5',_'value':_'option_5'}</t>
+          <t>feature_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 5', 'value': 'Option 5'}</t>
+          <t>Feature B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_6',_'value':_'option_6'}</t>
+          <t>feature_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 6', 'value': 'Option 6'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>page_3_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_'option_7',_'value':_'option_7'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 7', 'value': 'Option 7'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>page_7_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'option_8',_'value':_'option_8'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 8', 'value': 'Option 8'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>page_7_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'label':_'option_9',_'value':_'option_9'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 9', 'value': 'Option 9'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>page_8_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'option_10',_'value':_'option_10'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 10', 'value': 'Option 10'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>page_8_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'option_11',_'value':_'option_11'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 11', 'value': 'Option 11'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>page_9_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'label':_'option_12',_'value':_'option_12'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 12', 'value': 'Option 12'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>page_9_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'label':_'option_13',_'value':_'option_13'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 13', 'value': 'Option 13'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>page_10_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_'option_14',_'value':_'option_14'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 14', 'value': 'Option 14'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>page_10_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'option_15',_'value':_'option_15'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 15', 'value': 'Option 15'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>page_11_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'label':_'option_16',_'value':_'option_16'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 16', 'value': 'Option 16'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>page_11_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_'option_17',_'value':_'option_17'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 17', 'value': 'Option 17'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'label':_'option_18',_'value':_'option_18'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 18', 'value': 'Option 18'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>page_13_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'label':_'option_19',_'value':_'option_19'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 19', 'value': 'Option 19'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page_13_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page_14_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'label':_'option_20',_'value':_'option_20'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 20', 'value': 'Option 20'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>page_14_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'label':_'option_21',_'value':_'option_21'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 21', 'value': 'Option 21'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'label':_'option_22',_'value':_'option_22'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 22', 'value': 'Option 22'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'label':_'option_23',_'value':_'option_23'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 23', 'value': 'Option 23'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'label':_'option_24',_'value':_'option_24'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 24', 'value': 'Option 24'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'label':_'option_25',_'value':_'option_25'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 25', 'value': 'Option 25'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>Feature C</t>
         </is>
       </c>
     </row>
